--- a/tests/datos/Catalogo_con_errores.xlsx
+++ b/tests/datos/Catalogo_con_errores.xlsx
@@ -3555,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3567,8 +3567,10 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3585,6 +3587,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -3633,10 +3636,20 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
+          <t>Ancho puerta</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Alto puerta</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
           <t>Precio</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
@@ -3682,10 +3695,20 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
+          <t>m (puertas)</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>m (puertas)</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
           <t>€</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -3715,10 +3738,12 @@
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n">
         <v>449</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>tienda</t>
         </is>
@@ -3752,10 +3777,12 @@
       <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n">
         <v>593</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>tienda</t>
         </is>
@@ -3783,10 +3810,12 @@
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
       <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>estimado</t>
         </is>
@@ -3814,10 +3843,18 @@
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
       <c r="I9" s="9" t="inlineStr"/>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>tres</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="9" t="n">
         <v>420</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>estimado</t>
         </is>
@@ -3849,8 +3886,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>estimado</t>
         </is>
@@ -3882,8 +3921,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="9" t="inlineStr"/>
-      <c r="J11" s="9" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>estimado</t>
         </is>
@@ -3913,8 +3954,10 @@
       <c r="I12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>estimado</t>
         </is>
@@ -3925,7 +3968,7 @@
     <dataValidation sqref="B6:B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"motor,cuadro,puerta,ventana"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M6:M53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"fabricante,literatura,tienda,estimado"</formula1>
     </dataValidation>
   </dataValidations>
